--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,6 +1606,23 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>정은숙</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$eDj6juwPWwitSgVo$52eaeebed68d6c879abb027fb3f0aa56853ea81eeab96d89a7fe10375631655f6ea9e6097387fd6df6064e433d5abf139cbcb1c9c63d365091f199d407fdfb9e</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>정은숙.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,6 +1623,40 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>남궁석민</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$VxcMz7D1PdXdDcLS$4bd6ad489903ededaf0f2017bb0cd506f835459de9fc657da31cbdc62cdf00d9291bcf155b6b1cb180c941a8f12e61dcf4804f0b0b7f02104afb994a8099e503</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>남궁석민.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>이중배</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$3Dpxx9rVNAUTqvwp$1051923e580ce71b7caf5631b64c34a7a7a08a26b5bfb0f70145b2f048a4826aba1e5fa4af1527e34756a87de02b06affe5a0d3684d2927173a1c98cd0313bd8</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>이중배.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1657,6 +1657,57 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>김예지</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$ZlOcCGOUhNJeyLjB$24733755dd76102058a1fd7544dfd689b4e5536f5b9d81450b87b41b3fffc218b5671a68c362a09c6d69e823f1c89f01243ce96c3a93efd8ae5de88097733ec8</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>김예지.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>이상희</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$v3qUIPNsJVEwG2lW$83d130c3b632bbb76bcea427f952752148fc90ded713279e5120b4d2341a3f4d4b74bd37ce5de3e4fee6847a1f2875a7db6c6f85ed71960efdffa35ee0492b12</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>이상희.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>안광린</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$co3eU5POgQRG1j0W$45b43964b28a61b68a7b12e9cf0409612b0d7eee8e6913faf2e4b1817d22bc95adb62c9415b2c0c22166e2c409088a3cac08033514f67c6f3d60c80c08997102</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>안광린.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1708,6 +1708,40 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>송관식</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$lMnMzVC0g7hOuMST$426a38d60a1101ab058b2d564e57b782533deca0df96e7ebcb51a954e5ed88f9723bf9df4b265bb780dc0b4e4baa24515a1330ddc217fff560ebecda05f28404</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>송관식.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>장유진</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$DHUD0Yt5eWq8VTov$0cd4ba396cb68f1d5ae894c72fd0cfaca79e2548ce913a01238d2e1575e922b877abc194aa0c5c08ebcb5122acde6667d01a0c673164fb2c270eaef9d5063a39</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>장유진.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1742,6 +1742,23 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>김수정</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$khxchgFcjcCao7Vh$995670083996a8f1bf91d94a107d1834446f18e77604f9209998ade3037a95b0be1521812db5afc0e0eaef16fa9d73c97679a3a2259b145f80cdc672c8b6e501</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>김수정.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1759,6 +1759,74 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>박창열</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$l5RLzfZUCMVq3FvF$82d458489493371aa6b12bde3dfd2ffe5cc3c51bebf031d1d6c9cfcf9bf990d4b6275094077f44d13c3fc3877e98e8a39a4b8100508af2eb37b6829edcb850c6</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>박창열.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>현명한</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$QLzBuqcOB4i4c02B$881f897b3e9b7bbe73fd221498be8084381b0af5072e2204d1edced9315415fae01d8d9a5d34b89c57d222210d7289243e5d19213a194c5eb2a10dcba11c47d4</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>현명한.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>정미근</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$qo7MmuOkcfXjAl47$d8a9c2e5914cf9ebb0922c125f2cc9fc0374bbe8d500c23cebdbb41fb0a6679bf4770d5a04c83882726ddf4bc6dc7f18640e5496cacc3ec64a16c9ed69b89383</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>정미근.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>윤웅섭</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$0pnN8N2UP5YPU3Vs$309b3d40024ee29cfb46432404b522286cd2afa23e3372d63f50e612fc604c0b740aeb76221ceb5b9821339256180ec87039d1ae174cdc4e500f5dcf6c5f99b0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>윤웅섭.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1827,6 +1827,74 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>신동윤</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$jKPZJCVTTcFyAwmT$36d0806a1d747825fb1947bd98e7c210d1ec346312499e307b90d1eba056773dfbeb91b18868ec03ac378669dfcaf371ec01a9d2fa6fd5adf436d5ede1677e89</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>신동윤.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>정숙자</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$K3FdMNdHNn0UMRzC$022edd1c49a1e5454e4ca96323c0655d026041e386b2c05b4b0afe3d3faf19e7eb0ca7bda93c73883cede261c5b29a295932b37d22fbdf0d7e84a9095886b897</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>정숙자.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>임병희</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$ptNngIS3NxRFLfqI$9de0e81846eae4ad769dbb3e9a5ef145fec242177b8ab456a6e6bda1d66e6ac2b2fb1ffebf80bb3098478260d9391b8889e106ab096b352a953042a497256318</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>임병희.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>노성희</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$8KqYHeg81XedkKRF$9a927f645321f10afbf4bd292c8ec981dccd011b27e6dc1613c311c32bcb184f08e02913507efc896bc309ca694b2868038066c31ee5a0b7e038f818fcfe1e56</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>노성희.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,6 +1895,40 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>강경화</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$7g60FlLBRPZOVjeX$731919cb58a2baacbaf5bb64e8c2a41bf3a853600f14c59fb06235e2ac1c721c371795e529e5a2231a09b491164ce50ccf4a73f2ee860fc6f39e5575d0f3b157</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>강경화.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>김규홍</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$KJTZhlyrMF2jK6Xe$dbfd4efcca58d9b5727ae2905906fcef503abe55b26625d1eaa0036e20382bc8dfa30d6805b82b10804edc5f35531c616668d501d6830023bcdba1e00ed6c76b</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>김규홍.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1929,6 +1929,57 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>최종진</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$6hBuLURepB5W7vKm$775c732f6e19e722fca4c94dd068d95044d141ade5e36239618e80a73b9680dff81a91801d7a692d9be97900ce973b9dc91a388479fd860b4b7ee666c3ec40b5</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>최종진.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>백승록</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$ivQV65IJq3YNCza2$f2ff4846db37fdb34995529135375fa837b829a809fbb0d8a4f5523674539ac85e7f4711999ce5488f89c5828573fcdb1a84b613f66dad3fa7ce0607caad91ab</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>백승록.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>장원식</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$zjm62QsUcxpTwg7x$66298fb5cfeb0cb5fcda248ee617688919ff12c848696cd0412e44c203673ca49f842d7447e1bf34d3a5f92bebf967686f60e8f658e97ae974ee12db33448cee</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>장원식.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1980,6 +1980,23 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>조병훈</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$7yNlpF2s4jwSAHBU$1cb7d0225f3d07abd92fed7c5822cf72bc687082ced1b95687458591c7a1f6d50af52ad34d09f324cbc58818d537167948db783568fd86fa4a449e3840277591</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>조병훈.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1997,6 +1997,40 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>김경민</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$8f4LQ6rrWqVCqOGg$8b696ece7407ee4aa9a463cd787645d4913305df790139317f4f43d0096fddf447ca4dffa38cd7d32cfa1af5c62ca7fdfc36089b3d53f60530a62eff38c03cb5</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>김경민.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>전유라</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$T4JEA1Hp1iGCitZc$12113dfa728e7a61c16e18a05c05a7a282ec003c69f5459001a5f7256f1678198c5027d63ada1ad387602a5ec25d631ce7fb9e61e1e15c542fe7d52eeae290ad</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>전유라.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2031,6 +2031,40 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>김성수</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$6MVGWpV3rMWUil00$4c5a5492d2ad7cd8efb6d056b3fbed3aad7ff83a1e97463b2e49ff9d2595f9b049d10885bd4c025d3b09f11fc902cabafe42672b8dccbb41ad88d8d08831f900</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>김성수.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>임병인</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$BR5tdezYsy3SVPHe$1dad8443e13c83a0eb5a0bb30c4a8593860ca58433610733dfd64aae7bf36a94edabb25f33dfba84956ebe6fb95114f03ea8adae8039a7c11fea886ea46001c6</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>임병인.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2065,6 +2065,40 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>김만철</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$0Wy6wbnStKHaQDwL$5a8eb2b8664dc2a4e31a5f3ad2fa70ff29478c012fe5e31280964d1b37bb3252b4d62ef9085f6c33fed867853943e346127ffa597531a7f6f228f4a5a37c1dfd</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>김만철.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>김은경</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$b3wMoI7bseGQJmSb$7a484692dd6709f64abece80bec046f6d24f04948d8b8a1296e60c35517780de66ab12d8e6e51e5ef4f7d74aea8d63489717e0b28d031988b874d5941ac446c0</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>김은경.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2099,6 +2099,40 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>김미라</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$JNnglXJYw7nEgKWZ$8524f6e32cc178550605395cc6c5eddc12a0c8d54bd6bcc573a3f06a0382f299663495e9bd00fc903902279c3daa11b5ffbbd9ca3f92efe3fa17d79bbccef710</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>김미라.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>김광섭</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$wf66p4Cf8JQYv9W8$da75ecd39f998353f0393e152629a105582459d443a4a3f58c38e34aaf984aa2ba10421e996c29aee71069378c6f20e29f86df624263dc084eeea0abd53b337f</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>김광섭.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2133,6 +2133,312 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>김영원</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$4M7yqNso4Y9kZxg9$e63984fbd3cbf5e21ee5c2cfd9a9e32bdc19d55aae09b47b9bd2cf6478b134c4f627fe10d03bbde731027fd01dcfc5f8509e7dca0ba5456947f604c271313657</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>김영원.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>김정수</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$wbjir4Zt7KcB9vSz$8c26a1f69d6ba8f3cece7de8aacd97065ab02b23ce68990abe068d81a09b5d54715c0dc1ff13a09a98976d37381cea30cc9decd0e4726668d4124d845ae5615d</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>김정수.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>김정수1</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$JsJw6l93WetA1Xyw$1c443d48a0243a5cc6eb0991d874eae7658b7430be3788d31857b07e4711ab38f5d94468235af0413823f9333701ee2583dde166dd4852c66c74892bb263f3cd</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>김정수1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>우종오</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$AnzlPyYq90pyt62g$3cc047e2f67932ae3b376dd70127561763f9957521c11a2837fc3b5281abcbcdecc45acc5a28bd6f854d3dd41e714deac9b107178121a832cc445ecc8bff7b76</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>우종오.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>고성권</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$4ZJ2Ni7NOqFf3mZG$24412b2220c49aec89bdb9f527aea934c087001a038c04f80dd734483f82c4ffccb6b4e9d1ba7675a2304ba90a2542aa2882b24b392dda1228ce1e6a8c486af0</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>고성권.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>박해일</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$VXBptExyPseX2b0Z$cc203da87094eda47dd2fdad7f17d3fc49b9a6f592ecf206109136bcf7fbf22e1d29c0eb5846ad49fd438393a9c5266186effa7d4b076148e5c7e21c55e80ee3</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>박해일.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>이상준</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$8HjTdQkrBnILW3O5$2643b9a1ba6d7e049b01f1b964cca2fd8c1b33f56a241dd4f5bfaaf74643d86380010cc497f85d67ee6107d57aa7d36f4e13ccdd05f6427561512760e6332581</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>이상준.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>정남주</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$fEGTmtzPGE7yFZdf$28692f8ed34127ac96504ade632930cc3bfc61a2920ee651e01ea9a30bb051a3d9a437db56a1bbad69810a7b6ff728e7f06e7e4a657e7ff9108c558a6b70099f</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>정남주.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>이현상</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$x1vkchaj7OzALrkS$a4a6aa98550c11793872427d5efc59b12544bcee84ed11f83f97c862822f446cc081208e7563803fc4cd872afaf112b7b2aeb20301d1f0650716f06bbc8cd7ed</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>이현상.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>정원석</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$sfFAZ6A0qaWbMmUL$bc057cad4425b385ca92feeeb3dd8c65ba1dfb567def28a3926c0d1818b203306ca1afbc610d1df6df8263938d3e12f9de9258c06c2ac9f53afaa6fe104be558</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>정원석.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>신성희</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$Gsqb9tD5Ax0QrSdV$39d41e309ed0b8850aa9b5255ad605166d1579d89f343c8fdc5dcda8a44cab910b3e24c7b4af40c0906ce9d49a2809c4eadf8e290b268d792c52b37a93bf95f6</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>신성희.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>여유정</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$lB9qdUvGvLtNhr5U$26b5e3bb64fbd40c44cdcc390ccae17a9e4b0a220ec720925c752e1ea95745673b7d580227cd12ad2d4349326d8e20da4164d2015f6c132c159225a95404a084</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>여유정.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>조찬원</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$nH5KbaRLB2x9gCIO$f2d66501f4d9b2e185fcdadbc25beb2c54210da8e7ebfdb1753c98ab226022e24a40f90049c9f740cb137a6229bcbb9d1596561b02f39cf914b96152db9816a7</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>조찬원.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>최소영</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$QJOQ15iXAkaL59nX$ab37b81f4c4bcca898a4a7c6cb9cb93acfd402f554ed3ae92996e6d8c739b0de266565bc08cf1ab581908356c3caa9a59527a2d5d0a186f9288828091431dc6f</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>최소영.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>이미정</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$0deIxsQTvkILFIVS$f07d4bcda07f0b59e09f8bf1ea6af25e2500e2c8c8aa360640bc512a4560fe2b0d8323b4ce231fc07884689a735384091aa33585c91a3509278eca3fb74ea625</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>이미정.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>김영현</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$QGmrLeYo5gAH7crF$200621937681ec5a235d1d4dbf2d6547bf1af15dea9851ebf23da6f67f28767812b8803f862c58a4a800cda180a4b6a68b8721093c774f61e55080a20c3690c9</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>김영현.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>궁영균</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$wiZBlAUo5rnaiDrz$7c0e7674b714290536cf6122f96dda82490aa03ad7ba7599391229bb5321446a49826124b63d4e8901ea1ec9538e5ea5d4d742655202a86a22e010224c5253ab</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>궁영균.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>오세덕</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$3vK9KTqavwhvVVxa$c716405f2324a2550427c9507a953950e7fb2a2795eaf9f711a8bae52421115c54c99a8839f8e795d73bf89ef798971b328c135d563ace087ec1254edf6176d0</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>오세덕.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2439,6 +2439,108 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>문경조</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$veEhc49G7qnqu3eQ$622b4a063a18989a189e8cf5212ad9e210b811e2d66d1fe77c6575c3956b9a520d58bfe2180afaf4e486352a222f4bc6697ec7d395a400fe158c0634fb13696c</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>문경조.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>정유섭</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$NL1qauskzqwNTHa0$10e3330a1f847dbb56cfe254a7d5036a4f317688f91c39314a66496b57ecbfc4528a33a0973a1bb5abfa4e6cdb6becc3ec65bb250f086be60b504d63b8c7e954</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>정유섭.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>송진용</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$4tbSR6LHJd5mIIJA$61c760d3fe81ba58b7d57059252ef7143ee3fa2173448db1431928820e7287b4eef9692242e27e8ea223e7a966abd7b82aac87e208a2a6ba8c34abbbbba40c6d</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>송진용.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>김은영</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$cyIP9I2XrRgs0rQY$26ed3cb59d8c8143da0b0bb24b28ea88c5d2192ba69b226a41c6833dd6c99d54dc4562b90fb7ddcd3d10b858fb2cd8436f188ff3d160d1d04b914842ab3299d4</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>김은영.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>홍재현</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$ZxBLNOJx3ThmA8bK$41e825746967088bf5af2c89446d619172b3c370ef361bd6e6bc8d55eb0aef57d86441db0cf3d3cda988be6f316729948530661531feb9718d4dcbe346550216</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>홍재현.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>조영은</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$S7DKW6plFZE1AJii$c7c1b0d80c3e95d8e1cdb082a27aa92de2463988dbaa5a9b23de6daf6d83f0a6c1167df65c8b88bba74afcf43c2aab8c6d4167cdfc8d9ec5ebc893cb6a968534</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>조영은.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2541,6 +2541,23 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>임철웅</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$FJQZJ8PF08y5XA2s$bfee5e45a19c72c928df768b28a72da8c0a8e9ed41bb2ed825b368d93b5bcc82a46e500857e35950f9f12c12905d18a5405ed652d2fa7f6e8c0199aed3009e02</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>임철웅.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2558,6 +2558,74 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>김정숙</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$zYpnB8WOcdfjorQa$536b4654fc87b0b1cbae13fb8d2c6c6f5cef590987c7691de6541cbaa2dbfb2a1cbdad0250a3860bc410da3dab049db70ba9534767607f9dc405e8009a607d30</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>김정숙.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>문보성</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$Id8Jrw3bnha8kwW2$c32a886ac3efbab086530b5e8b0be58c925c2daecfc857bb02fb51bdafe6c5a839c4cad7cf97bd57258df4d9345ad081ae2dd4021a445de0ad5b49986dafc9a0</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>문보성.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>이강현</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$wagsbwU8lxDSzZyf$fda01398ea01a8acf3f4882675061d996716dcd56551bd29e7b1bfe196ba79bdeae62c5eacefd1d282289a0f62aa49c65de9a9ad84a35a2001c303d041f0321b</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>이강현.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>김준영</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$QXu2F8mz4eISTUBz$ae31d2a74465b13427692a4e72f4c223ea1d9ff5adeddafddb34e298f00c6818aa152f4a9f628b03ed58d80988c8c230db5467e0c6bff6b034ba773a96479c38</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>김준영.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2626,6 +2626,40 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>윤희지</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$2LBC6VR01Yt8wkm3$a337c825e9a026864120d6bb7d52fb52d6175d5681e51904da39f78114c6663e600dccdbc5fbd8459457ccc0762660f42532f264ed4683895bd266c4dfd29c8e</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>윤희지.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>오진혁</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$xgk9r54ronTwwiZC$d0254fc6a7098cc142eef8c0490007e792d272cf8bfa189dd8d938041d8e1b5878a9f8d0caeebb2578baac5dc1664a3d6abc0e9b00c403c37dbfb6386708fd40</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>오진혁.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2660,6 +2660,23 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>서하늘</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$AJf9lrdMSU3CztxC$afe3b810aedb1814e4088be04cadb7e51e372af251da284c18c0a4fc2903d7a7f74deb99863d504d85438749a3ebc8f97637eb5188b7b8acdf0dd2c5cae36fb6</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>서하늘.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_2026.xlsx
+++ b/users_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2677,6 +2677,159 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>정해윤</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$UGHO1OrmISTID7Dv$7d5e92369959924739e57a164778c1d9debf743810fe5f6786e6318836dfdf334c376dbad42826553640eb265705e39faa4a3b1550b26b4720c1a9a3ffa2b868</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>정해윤.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>조동열</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$XnE0WuVrffsCqbzu$3f0303d1e29682f5d608e7c96328ab2d83acc709099413f76fa1769bea9e57dd7a0e1c9741af9315f5d4e1a68c61b6cf1e652588fc8cbf3cbacc9c9d9762e888</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>조동열.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>박은영</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$8mdHZekmi4K6sCJN$145eea58861806d66d46bc3918d84ab32211e3a49478f27c807bfe38d8da0147c423900de85ea7a3a0d19f5a5077d1e4cbff5eda155e2e23998320804728015d</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>박은영.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>강성하</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$w86e5Z2BR2BS4ZNa$d11c4389fdd9cef52eb5f1ef55662b4fff7e5ee7ed0882b6ae970bd737d2dc2e97fd73aa86f82d420ce6054492c54ba9cf8407672ce94439fbf7738a91a98c12</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>강성하.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>남준철</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$qvIccbjqJoCcQicU$d236ca2eff96c6c8aaeeebd2d56ebe434f3055db03141201c2b1788949b63427a224264f2beaaa34aafc8a1b355e475b213cbccb3243a8ce7fc8b2fab9e22614</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>남준철.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>박성웅</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$V1sYAMKmQ5dUwuNi$426d4e06812044af3346132a2da92054759b9e8d4e00be603aa5fd191155f0f63659e63bebde9678cd225a0980d9253f41253d35b759f4de5d7be5bbb95bd964</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>박성웅.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>박병민</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$uVDdi0qCx3NZO83p$9c7ba9046416643bf5b7c24d44088afa4bacc3ddb1f43b4678005ea2122ecf70f7558cea4b049ee619d53d3d42fd074ced7095ee020beab21737e4ddc268557b</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>박병민.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>한형선</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$4Krk0KtP1VLAjSFf$fd1147076912a207e62a33b0d6b1390f43c917f01e02a762a2368886963b55d4b379dd3fe19100b3689b7e774f32fe0baa2b5fc80f2393f60b5552c95a0dc588</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>한형선.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>피경희</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$HBnkaVy9hbg2FYT1$3a3725eb424358000d9db05fca7a85b34293b7b80ee4ae5530a76566b37c37f025e14b3aadfbcfcabf384cd6e9bd9b90b45be8e8e84e1ec5015bb4f7aea56f78</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>피경희.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
